--- a/Paper2_Package/03_RESULTS/Task2_drug_gene_extraction/task2_supporting.xlsx
+++ b/Paper2_Package/03_RESULTS/Task2_drug_gene_extraction/task2_supporting.xlsx
@@ -1552,7 +1552,7 @@
         <v>55.9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.778</v>
+        <v>0.553</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>56.1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.74</v>
+        <v>0.609</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>55.9</v>
       </c>
       <c r="G4" t="n">
-        <v>0.77</v>
+        <v>0.572</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>56.1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.731</v>
+        <v>0.632</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>58.3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.512</v>
+        <v>1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>56.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.248</v>
+        <v>0.485</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>10000</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7778</v>
+        <v>0.553</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
